--- a/result/train_info_googlenet_part_detrend_plr_stft_bin_win_anova.xlsx
+++ b/result/train_info_googlenet_part_detrend_plr_stft_bin_win_anova.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3477947479404542</v>
+        <v>0.3616410059325763</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2054551779650725</v>
+        <v>0.1784938887290701</v>
       </c>
       <c r="E2" t="n">
-        <v>0.924563359345968</v>
+        <v>0.9321813452248234</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9889078498293515</v>
+        <v>0.9649262654444002</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8591549295774648</v>
+        <v>0.8973313565604151</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9194763982546609</v>
+        <v>0.929902054926061</v>
       </c>
       <c r="I2" t="n">
-        <v>70.89748215675354</v>
+        <v>69.70944809913635</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1144247234675806</v>
+        <v>0.1230887089251232</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05262041513631727</v>
+        <v>0.06086228805120219</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9808621330360461</v>
+        <v>0.979933110367893</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9901775595013222</v>
+        <v>0.9853823088455772</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9714603409933283</v>
+        <v>0.9744255003706449</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9807296538821328</v>
+        <v>0.9798732761833768</v>
       </c>
       <c r="I3" t="n">
-        <v>69.47675323486328</v>
+        <v>65.294842004776</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05319112933667745</v>
+        <v>0.06051313642752848</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05273069191679976</v>
+        <v>0.05715214235490441</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9816053511705686</v>
+        <v>0.9806763285024155</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9865219019093973</v>
+        <v>0.9685693641618497</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9766493699036323</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9815608120692867</v>
+        <v>0.9809732894255397</v>
       </c>
       <c r="I4" t="n">
-        <v>69.84014177322388</v>
+        <v>67.55708789825439</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04284806224520292</v>
+        <v>0.04099388160342544</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05522800386007104</v>
+        <v>0.03862294428117336</v>
       </c>
       <c r="E5" t="n">
-        <v>0.976960237829803</v>
+        <v>0.9868078781122259</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9619526202440776</v>
+        <v>0.9816648331499817</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9773887673231219</v>
+        <v>0.9869124423963134</v>
       </c>
       <c r="I5" t="n">
-        <v>69.83853721618652</v>
+        <v>67.38793659210205</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.029974618295355</v>
+        <v>0.03424984029487134</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03921352651489612</v>
+        <v>0.05186781282026938</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9866220735785953</v>
+        <v>0.9836492010405053</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9813049853372434</v>
+        <v>0.9887640449438202</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9922164566345441</v>
+        <v>0.9785025945144552</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9867305565794323</v>
+        <v>0.9836065573770492</v>
       </c>
       <c r="I6" t="n">
-        <v>70.03281736373901</v>
+        <v>65.07890748977661</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02601448167755475</v>
+        <v>0.03035836281674536</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02037511951575598</v>
+        <v>0.0633255630273843</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9946116685247121</v>
+        <v>0.9795615013006317</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9948090470893586</v>
+        <v>0.9799703264094956</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.9792438843587843</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9946246524559778</v>
+        <v>0.9796069707081942</v>
       </c>
       <c r="I7" t="n">
-        <v>69.75996780395508</v>
+        <v>64.55472564697266</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02284410769608699</v>
+        <v>0.02181530511151583</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03199126873407843</v>
+        <v>0.05081263104899367</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9869936826458565</v>
+        <v>0.9816053511705686</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9906646751306946</v>
+        <v>0.9898228420655861</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9833209785025945</v>
+        <v>0.9733135656041513</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9869791666666666</v>
+        <v>0.9814987852737806</v>
       </c>
       <c r="I8" t="n">
-        <v>69.71344757080078</v>
+        <v>58.33244562149048</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02417239288427429</v>
+        <v>0.02786511240065092</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0450589942384908</v>
+        <v>0.06545468657167308</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9858788554440728</v>
+        <v>0.9803047194351542</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9746560463432296</v>
+        <v>0.9726477024070022</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9885100074128984</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9860805860805861</v>
+        <v>0.9805147058823529</v>
       </c>
       <c r="I9" t="n">
-        <v>69.91212034225464</v>
+        <v>54.72993659973145</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02122574393653219</v>
+        <v>0.0189062169074059</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02865307061356415</v>
+        <v>0.02208458046847679</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9910813823857302</v>
+        <v>0.9914529914529915</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9925650557620818</v>
+        <v>0.9955156950672646</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9896219421793921</v>
+        <v>0.9873980726464048</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9910913140311804</v>
+        <v>0.9914402679568292</v>
       </c>
       <c r="I10" t="n">
-        <v>70.01705551147461</v>
+        <v>59.70766258239746</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01819825415987268</v>
+        <v>0.02396181401525104</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01641460957852731</v>
+        <v>0.02833506580546895</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9914529914529915</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9944547134935305</v>
+        <v>0.9896602658788775</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9957431056820285</v>
+        <v>0.9914909359970403</v>
       </c>
       <c r="I11" t="n">
-        <v>70.83522605895996</v>
+        <v>49.8324031829834</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01316074187129953</v>
+        <v>0.01384474336519339</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01838434294957809</v>
+        <v>0.02740297599068083</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9903381642512077</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9911537043862882</v>
+        <v>0.9940253920836445</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9866567828020756</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9939013121419331</v>
+        <v>0.9903273809523809</v>
       </c>
       <c r="I12" t="n">
-        <v>71.02567028999329</v>
+        <v>48.28144574165344</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01797229983627703</v>
+        <v>0.01669356652551088</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02908733529342682</v>
+        <v>0.0250301767523282</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9886659234485321</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9936353425683264</v>
+        <v>0.9922193404964802</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9836916234247591</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9886384801639039</v>
+        <v>0.9924031869557162</v>
       </c>
       <c r="I13" t="n">
-        <v>71.9382004737854</v>
+        <v>47.38718008995056</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01436625184995091</v>
+        <v>0.01431365642455918</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03160851944676055</v>
+        <v>0.02460670360022093</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9903381642512077</v>
+        <v>0.9918246005202527</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9969947407963937</v>
+        <v>0.9922106824925816</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9836916234247591</v>
+        <v>0.991475166790215</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9902985074626866</v>
+        <v>0.9918427882832778</v>
       </c>
       <c r="I14" t="n">
-        <v>72.37477135658264</v>
+        <v>46.73002910614014</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01448334754325259</v>
+        <v>0.01566997718481431</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01422136344721495</v>
+        <v>0.01400631451900062</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9926226484691996</v>
+        <v>0.9966555183946488</v>
       </c>
       <c r="G15" t="n">
-        <v>0.997405485544848</v>
+        <v>0.994069681245367</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9950083194675541</v>
+        <v>0.995360920393394</v>
       </c>
       <c r="I15" t="n">
-        <v>72.19091629981995</v>
+        <v>45.38061141967773</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01266742509267007</v>
+        <v>0.01086271494543385</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02209198084772157</v>
+        <v>0.01505758027676472</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9915129151291513</v>
+        <v>0.9951780415430267</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9944403261675315</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9937130177514792</v>
+        <v>0.9948090470893586</v>
       </c>
       <c r="I16" t="n">
-        <v>71.62893676757812</v>
+        <v>45.3376681804657</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01133310751532969</v>
+        <v>0.01217736918559856</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01810164183768108</v>
+        <v>0.01124134885205594</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9966555183946488</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9948128936643201</v>
+        <v>0.9955621301775148</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9951816160118606</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9949972206781545</v>
+        <v>0.9966679007774898</v>
       </c>
       <c r="I17" t="n">
-        <v>71.06006097793579</v>
+        <v>45.63070917129517</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0100354954899962</v>
+        <v>0.01366049251177671</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0850796741744069</v>
+        <v>0.03113766357553406</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9812337421033073</v>
+        <v>0.9875510962467484</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9686033922771563</v>
+        <v>0.9954802259887006</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9796145292809488</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9815322728103858</v>
+        <v>0.98748365402578</v>
       </c>
       <c r="I18" t="n">
-        <v>70.87301421165466</v>
+        <v>45.70504713058472</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01359775258061647</v>
+        <v>0.01232154511013575</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02151003495818307</v>
+        <v>0.01531638737001419</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9936826458565589</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9940520446096655</v>
+        <v>0.9922394678492239</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9911045218680504</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9925760950259837</v>
+        <v>0.9937083641746854</v>
       </c>
       <c r="I19" t="n">
-        <v>70.56908774375916</v>
+        <v>45.47855663299561</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01078716943651195</v>
+        <v>0.01123314571530359</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02602387624425943</v>
+        <v>0.0354384780463111</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9933110367892977</v>
+        <v>0.9875510962467484</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9944279346210996</v>
+        <v>0.982044705020154</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9922164566345441</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9933209647495361</v>
+        <v>0.9876543209876543</v>
       </c>
       <c r="I20" t="n">
-        <v>70.80141305923462</v>
+        <v>44.36508822441101</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.008483709195195406</v>
+        <v>0.01191990667952509</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01528958050754044</v>
+        <v>0.01146659785253495</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9947974730583427</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9929837518463811</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9948205697373289</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="I21" t="n">
-        <v>70.32059216499329</v>
+        <v>43.22335577011108</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.008438830174395695</v>
+        <v>0.007595243778868947</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01359282376179396</v>
+        <v>0.01972295256235038</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9960981047937569</v>
+        <v>0.9946116685247121</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9948243992606285</v>
+        <v>0.9970204841713222</v>
       </c>
       <c r="G22" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9961132704053304</v>
+        <v>0.9946126695151403</v>
       </c>
       <c r="I22" t="n">
-        <v>70.26239514350891</v>
+        <v>43.22804069519043</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.00994541699834442</v>
+        <v>0.006450136691419067</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01906441476164364</v>
+        <v>0.02050032283566035</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9931252322556671</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9951672862453531</v>
+        <v>0.9915035094200222</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9922164566345441</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9936896807720861</v>
+        <v>0.993154486586494</v>
       </c>
       <c r="I23" t="n">
-        <v>70.33665204048157</v>
+        <v>43.40711998939514</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00928402642414106</v>
+        <v>0.009496391371543922</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02313483011116309</v>
+        <v>0.01996915814469874</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9901523597175771</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9907783105864995</v>
+        <v>0.9932860872808653</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9870274277242401</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9931595488999815</v>
+        <v>0.9901468674474809</v>
       </c>
       <c r="I24" t="n">
-        <v>70.09824466705322</v>
+        <v>43.33204674720764</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.007265499982135533</v>
+        <v>0.01005857692422963</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0173786216565806</v>
+        <v>0.0267961460776537</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9918246005202527</v>
       </c>
       <c r="F25" t="n">
-        <v>0.996274217585693</v>
+        <v>0.9875091844232182</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9911045218680504</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9918819188191882</v>
       </c>
       <c r="I25" t="n">
-        <v>69.9422299861908</v>
+        <v>43.37239933013916</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.009297480205417468</v>
+        <v>0.007451698287120064</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.04613554400179023</v>
+        <v>0.009470745977685069</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9869936826458565</v>
+        <v>0.99702712746191</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9884758364312267</v>
+        <v>0.9944690265486725</v>
       </c>
       <c r="G26" t="n">
-        <v>0.985544848035582</v>
+        <v>0.9996293550778355</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9870081662954714</v>
+        <v>0.9970425138632163</v>
       </c>
       <c r="I26" t="n">
-        <v>70.15699362754822</v>
+        <v>43.19283366203308</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.007006877929103363</v>
+        <v>0.007748362400355359</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01685637251618449</v>
+        <v>0.01494067964783302</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F27" t="n">
-        <v>0.990791896869245</v>
+        <v>0.9977670264235207</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9939035654904859</v>
+        <v>0.9957288765088208</v>
       </c>
       <c r="I27" t="n">
-        <v>69.9593665599823</v>
+        <v>43.48280644416809</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.00792646073806345</v>
+        <v>0.005802431656810434</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03302011295170427</v>
+        <v>0.01799099435032254</v>
       </c>
       <c r="E28" t="n">
-        <v>0.990709773318469</v>
+        <v>0.9936826458565589</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9947683109118086</v>
+        <v>0.9973861090365945</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9866567828020756</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="H28" t="n">
-        <v>0.990695943431336</v>
+        <v>0.9936755952380952</v>
       </c>
       <c r="I28" t="n">
-        <v>70.04311609268188</v>
+        <v>45.78466033935547</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.004607398637063957</v>
+        <v>0.007129295586851949</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01128471926837239</v>
+        <v>0.01646482899351756</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.9944258639910813</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9951940850277264</v>
+        <v>0.9962797619047619</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9964834351286322</v>
+        <v>0.9944300037133309</v>
       </c>
       <c r="I29" t="n">
-        <v>70.0092294216156</v>
+        <v>46.54323554039001</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0092403084586612</v>
+        <v>0.006152017503850611</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.024513509966279</v>
+        <v>0.01714344318244815</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9944196428571429</v>
+        <v>0.9985074626865672</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9907338769458859</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9925733382844412</v>
+        <v>0.995165489029379</v>
       </c>
       <c r="I30" t="n">
-        <v>70.07611751556396</v>
+        <v>46.49060416221619</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.006396890023081295</v>
+        <v>0.005082121617094086</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02208516629252699</v>
+        <v>0.003840221926342963</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9983277591973244</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9882568807339449</v>
+        <v>0.9977786005183266</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9988880652335063</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9931772081873502</v>
+        <v>0.9983330246341915</v>
       </c>
       <c r="I31" t="n">
-        <v>70.15853905677795</v>
+        <v>46.16598463058472</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.004785484671962889</v>
+        <v>0.007815984936726137</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01128180543926743</v>
+        <v>0.01002928820403294</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9972129319955407</v>
+        <v>0.9959123002601263</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9970359392367544</v>
+        <v>0.9955555555555555</v>
       </c>
       <c r="G32" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9972206781545303</v>
+        <v>0.9959244164505372</v>
       </c>
       <c r="I32" t="n">
-        <v>69.96743822097778</v>
+        <v>46.26566481590271</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.004367488863055261</v>
+        <v>0.003522730082807493</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01833607451117562</v>
+        <v>0.01596416370102277</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9959153360564427</v>
+        <v>0.9944444444444445</v>
       </c>
       <c r="G33" t="n">
-        <v>0.994069681245367</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H33" t="n">
-        <v>0.994991652754591</v>
+        <v>0.9948128936643201</v>
       </c>
       <c r="I33" t="n">
-        <v>70.10502076148987</v>
+        <v>45.7740843296051</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1396,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.003579798352465241</v>
+        <v>0.004762733791305753</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02485246458921549</v>
+        <v>0.01186918480883155</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9966455460305628</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9911045218680504</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H34" t="n">
-        <v>0.993867310908753</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="I34" t="n">
-        <v>70.94275498390198</v>
+        <v>45.93810200691223</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.006141528729282453</v>
+        <v>0.005644692493605433</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.02729578364691535</v>
+        <v>0.01583180634462175</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9927536231884058</v>
+        <v>0.9942400594574508</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9893264630106735</v>
+        <v>0.9907986750092014</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H35" t="n">
-        <v>0.992797783933518</v>
+        <v>0.994275161588181</v>
       </c>
       <c r="I35" t="n">
-        <v>71.73427128791809</v>
+        <v>45.80555176734924</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.002946470310342309</v>
+        <v>0.004072458130056956</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.01621505204367604</v>
+        <v>0.01040185706159928</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.9966555183946488</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9959274342835986</v>
+        <v>0.9959289415247965</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9964808297832932</v>
+        <v>0.9966666666666667</v>
       </c>
       <c r="I36" t="n">
-        <v>71.59615540504456</v>
+        <v>45.8962140083313</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.007278217252329384</v>
+        <v>0.006486593132053462</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01459957342361515</v>
+        <v>0.01517927393612308</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9947974730583427</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9929837518463811</v>
+        <v>0.9951798294401186</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9948205697373289</v>
+        <v>0.9949953660797034</v>
       </c>
       <c r="I37" t="n">
-        <v>71.87129306793213</v>
+        <v>45.87227725982666</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.003945546906157299</v>
+        <v>0.006595127018173261</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.01338841402386778</v>
+        <v>0.03184231708016379</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.989223337049424</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9904517076753581</v>
+        <v>0.9817518248175182</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9996293550778355</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9950193691200886</v>
+        <v>0.9893343140860611</v>
       </c>
       <c r="I38" t="n">
-        <v>71.93458271026611</v>
+        <v>45.7140781879425</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.002904334555755174</v>
+        <v>0.005339759869980332</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01216039307558723</v>
+        <v>0.008885357572327751</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9973987365291713</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9933628318584071</v>
+        <v>0.9948377581120944</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9985174203113417</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9959334565619223</v>
+        <v>0.9974121996303142</v>
       </c>
       <c r="I39" t="n">
-        <v>71.50952219963074</v>
+        <v>45.78098773956299</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.00301184269203089</v>
+        <v>0.003682156993529152</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0170069418717713</v>
+        <v>0.01625413400151606</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9944258639910813</v>
+        <v>0.9947974730583427</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9918879056047197</v>
+        <v>0.9940784603997039</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9944547134935305</v>
+        <v>0.9948148148148148</v>
       </c>
       <c r="I40" t="n">
-        <v>70.95743918418884</v>
+        <v>45.59379100799561</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>0.003708912445717523</v>
+        <v>0.001432027690384023</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0153515477766729</v>
+        <v>0.0116436955775272</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9962839093273876</v>
+        <v>0.9960981047937569</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9948263118994827</v>
+        <v>0.9926389400073611</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9996293550778355</v>
       </c>
       <c r="H41" t="n">
-        <v>0.996299037749815</v>
+        <v>0.9961218836565097</v>
       </c>
       <c r="I41" t="n">
-        <v>70.72173380851746</v>
+        <v>45.83366584777832</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>9.667771449007016e-05</v>
+        <v>0.004695410361740704</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01523632504801199</v>
+        <v>0.02781035147298895</v>
       </c>
       <c r="E42" t="n">
-        <v>0.99702712746191</v>
+        <v>0.9934968413229283</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9959319526627219</v>
+        <v>0.9897020963589555</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9970381340244354</v>
+        <v>0.9935388591471294</v>
       </c>
       <c r="I42" t="n">
-        <v>70.47950744628906</v>
+        <v>45.79849934577942</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>1.285561138834872e-05</v>
+        <v>0.003842773350989729</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01754805626717909</v>
+        <v>0.008481573683934988</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9977703455964325</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9959304476507584</v>
+        <v>0.9981454005934718</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9968524347343085</v>
+        <v>0.9977753058954394</v>
       </c>
       <c r="I43" t="n">
-        <v>70.09946465492249</v>
+        <v>45.88071012496948</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>4.495958972254603e-06</v>
+        <v>0.00134558332331127</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01732303723975123</v>
+        <v>0.008121071396235278</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9975845410628019</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9959304476507584</v>
+        <v>0.9981447124304267</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9968524347343085</v>
+        <v>0.9975894678286668</v>
       </c>
       <c r="I44" t="n">
-        <v>69.79593467712402</v>
+        <v>46.10167670249939</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>3.53093848236568e-06</v>
+        <v>0.0005704683539353605</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.02414186340464855</v>
+        <v>0.01086854074171549</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9972129319955407</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9959304476507584</v>
+        <v>0.9966679007774898</v>
       </c>
       <c r="G45" t="n">
         <v>0.9977761304670126</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9968524347343085</v>
+        <v>0.9972217077236525</v>
       </c>
       <c r="I45" t="n">
-        <v>70.03971481323242</v>
+        <v>45.85590744018555</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>1.414969804052297e-06</v>
+        <v>0.005637683635962142</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.02219687438037937</v>
+        <v>0.006787943100542007</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9966555183946488</v>
+        <v>0.9975845410628019</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9962962962962963</v>
+        <v>0.999256229081443</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9966654316413487</v>
+        <v>0.9975867829961017</v>
       </c>
       <c r="I46" t="n">
-        <v>70.11249923706055</v>
+        <v>45.86195588111877</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>1.501562758526675e-06</v>
+        <v>0.001677978708653799</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01905179429715615</v>
+        <v>0.009990636701883439</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9975845410628019</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9966654316413487</v>
+        <v>0.9988851727982163</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9968501019084677</v>
+        <v>0.9975876786045649</v>
       </c>
       <c r="I47" t="n">
-        <v>69.82639837265015</v>
+        <v>45.92053890228271</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.008802046815122757</v>
+        <v>0.003486776547740082</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01692786960979337</v>
+        <v>0.02415285450698164</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9953548866592344</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9933554817275747</v>
+        <v>0.9985041136873598</v>
       </c>
       <c r="G48" t="n">
-        <v>0.997405485544848</v>
+        <v>0.9896219421793921</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9953763639726281</v>
+        <v>0.9940431868950111</v>
       </c>
       <c r="I48" t="n">
-        <v>70.67641615867615</v>
+        <v>46.15721440315247</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.004880704116235318</v>
+        <v>0.001404606183579723</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.01236722278478883</v>
+        <v>0.008549600620336504</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9962839093273876</v>
+        <v>0.9979561501300632</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9959259259259259</v>
+        <v>0.9981460882461994</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9962949240459429</v>
+        <v>0.9979610750695088</v>
       </c>
       <c r="I49" t="n">
-        <v>71.01773166656494</v>
+        <v>46.05891609191895</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.001765605479284104</v>
+        <v>4.077412021136528e-05</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.01561852702129538</v>
+        <v>0.009206557428892693</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9977703455964325</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9933603836222796</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9957478276945831</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="I50" t="n">
-        <v>71.56226372718811</v>
+        <v>45.96846079826355</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.001389883282764968</v>
+        <v>1.493893414890962e-05</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01424054504996523</v>
+        <v>0.009070845282014579</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9959123002601263</v>
+        <v>0.9981419546636938</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9937269372693727</v>
+        <v>0.9985163204747775</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9959319526627219</v>
+        <v>0.9981460882461994</v>
       </c>
       <c r="I51" t="n">
-        <v>71.33444976806641</v>
+        <v>45.86849498748779</v>
       </c>
     </row>
   </sheetData>
